--- a/NBFC-MF/Borrowers/Salam_Echan_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Salam_Echan_Weekly.xlsx
@@ -749,31 +749,33 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="22" t="str">
+      <c r="A2" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B2" s="22">
         <f>IF(A2&lt;&gt;"",1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="1">
         <f t="shared" ref="D2:D18" si="0">IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E2" s="1" t="str">
+        <v>1400</v>
+      </c>
+      <c r="E2" s="1">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F2" s="1" t="str">
+        <v>401.03124158893064</v>
+      </c>
+      <c r="F2" s="1">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),D2-E2,"")</f>
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
+        <v>998.9687584110693</v>
+      </c>
+      <c r="G2" s="1">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-F2,"")</f>
-        <v/>
-      </c>
-      <c r="H2" s="1" t="str">
+        <v>19001.031241588931</v>
+      </c>
+      <c r="H2" s="1">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-G2,"")</f>
-        <v/>
+        <v>998.96875841106885</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>17</v>
@@ -1116,7 +1118,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1151,7 +1153,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>23800</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1186,7 +1188,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>23800</v>
+        <v>19001.031241588931</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1221,7 +1223,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>0</v>
+        <v>998.96875841106885</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1254,9 +1256,9 @@
       <c r="J16" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="16" t="str">
+      <c r="K16" s="16">
         <f>IF(A2,A2, "")</f>
-        <v/>
+        <v>46202</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -1289,9 +1291,9 @@
       <c r="J17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="18" t="str">
+      <c r="K17" s="18">
         <f xml:space="preserve"> IF(A2,(K16 + (17*7)),"")</f>
-        <v/>
+        <v>46321</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Salam_Echan_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Salam_Echan_Weekly.xlsx
@@ -791,31 +791,33 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="23" t="str">
+      <c r="A3" s="19">
+        <v>46209</v>
+      </c>
+      <c r="B3" s="23">
         <f>IF(A3&lt;&gt;"",B2+1,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C3" s="20"/>
-      <c r="D3" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E3" s="21" t="str">
+      <c r="D3" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E3" s="21">
         <f t="shared" ref="E3:E18" si="1">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F3" s="21" t="str">
+        <v>381.00035751422342</v>
+      </c>
+      <c r="F3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),D3-E3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="21" t="str">
+        <v>1018.9996424857766</v>
+      </c>
+      <c r="G3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2-F3,"")</f>
-        <v/>
-      </c>
-      <c r="H3" s="21" t="str">
+        <v>17982.031599103153</v>
+      </c>
+      <c r="H3" s="21">
         <f t="shared" ref="H3:H18" si="2">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),$K$7-G3,"")</f>
-        <v/>
+        <v>2017.968400896847</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>10</v>
@@ -1118,7 +1120,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1153,7 +1155,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>22400</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1188,7 +1190,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>19001.031241588931</v>
+        <v>17982.031599103153</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1223,7 +1225,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>998.96875841106885</v>
+        <v>2017.968400896847</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Salam_Echan_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Salam_Echan_Weekly.xlsx
@@ -827,31 +827,33 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="22" t="str">
+      <c r="A4" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B4" s="22">
         <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F4" s="1" t="str">
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="1"/>
+        <v>360.56782292398606</v>
+      </c>
+      <c r="F4" s="1">
         <f t="shared" ref="F4:F18" si="4">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="str">
+        <v>1039.4321770760139</v>
+      </c>
+      <c r="G4" s="1">
         <f t="shared" ref="G4:G18" si="5">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>16942.599422027139</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="2"/>
+        <v>3057.4005779728614</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>11</v>
@@ -1120,7 +1122,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1155,7 +1157,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>21000</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1190,7 +1192,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>17982.031599103153</v>
+        <v>16942.599422027139</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1225,7 +1227,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>2017.968400896847</v>
+        <v>3057.4005779728614</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
